--- a/Map_village_20241227.xlsx
+++ b/Map_village_20241227.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="28730"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30026"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\simon\Desktop\disk c bureau\Enseignement\2A - M1\SG8 Innovation durable\Projet SG8 innovation durable\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/d36960ecafd59629/Desktop/centrale/Block Week/"/>
     </mc:Choice>
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2E8E7664-552E-4386-8508-C945CE6E214C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="19090" yWindow="-760" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -506,7 +506,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:J202"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="17.42578125" style="1" customWidth="1"/>
     <col min="2" max="2" width="12.7109375" style="1" bestFit="1" customWidth="1"/>
